--- a/practice-files/day02-数据输入与格式.xlsx
+++ b/practice-files/day02-数据输入与格式.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据类型练习" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ctrl+E练习" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据类型练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ctrl+E练习" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -570,19 +569,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -742,7 +728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/practice-files/day02-数据输入与格式.xlsx
+++ b/practice-files/day02-数据输入与格式.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -526,33 +526,40 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1. A列是"姓名+手机号"的合并数据</t>
+          <t>WPS提示：WPS里叫"智能填充"，快捷键一样是Ctrl+E（需WPS 2019及以上版本）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2. 在B1手打第一行的名字（张三），B2手打第二行的名字（李四）</t>
+          <t>1. A列是"姓名+手机号"的合并数据</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3. 选中B1:B2→按Ctrl+E→Excel自动补全所有名字</t>
+          <t>2. 在B1手打第一行的名字（张三），B2手打第二行的名字（李四）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4. 同样方法在C列提取手机号</t>
+          <t>3. 选中B1:B2→按Ctrl+E→Excel自动补全所有名字</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4. 同样方法在C列提取手机号</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>5. 试试反过来：在D列把名字和手机号用"-"重新合并（如"张三-13800138001"）</t>
         </is>

--- a/practice-files/day02-数据输入与格式.xlsx
+++ b/practice-files/day02-数据输入与格式.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -87,16 +103,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -562,6 +583,41 @@
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>5. 试试反过来：在D列把名字和手机号用"-"重新合并（如"张三-13800138001"）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 文本"123"和数字123在筛选时有什么不同？怎么一眼分辨？</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" hidden="1" outlineLevel="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 筛选"大于100"时只有数字123会被筛出来，文本"123"不参与数值比较。一眼分辨看对齐方式：文本左对齐、数字右对齐（左上角有绿色小三角提示的也是文本）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: Ctrl+E（智能填充）什么时候会失灵？补完后必须做什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" hidden="1" outlineLevel="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 数据没有统一规律时，补出来的结果是错的。补完之后必须从上到下扫一眼全部结果，不对的单元格手动改。</t>
         </is>
       </c>
     </row>
@@ -585,150 +641,150 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>文本型数据</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>数字型数据</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>日期型数据</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>'00123（文本）</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>'00456（文本）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="7" t="n">
         <v>456</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>'00789（文本）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="7" t="n">
         <v>789.5</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>'员工编号A001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>'商品SKU-B123</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="7" t="n">
         <v>2500.99</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>'订单NO-2026</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="7" t="n">
         <v>-150</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>'用户ID:8888</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>'备注：已发货</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="7" t="n">
         <v>8888.879999999999</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>← 试试在这里输入不同类型的数据</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -751,180 +807,180 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>姓名+手机号（合并列）</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>姓名（Ctrl+E拆分）</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>手机号（Ctrl+E拆分）</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>重新合并（Ctrl+E）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>张三13800138001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>提示：在B列和C列先用Ctrl+E拆分，再在D列试试合并</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>李四13900139002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>王五13700137003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>赵六13600136004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>孙七13500135005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>周八13400134006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>吴九13300133007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>郑十13200132008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>钱十一13100131009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>冯十二15000150010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>陈十三15100151011</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>褚十四15200152012</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>卫十五15300153013</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>蒋十六15500155014</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>沈十七15600156015</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/practice-files/day02-数据输入与格式.xlsx
+++ b/practice-files/day02-数据输入与格式.xlsx
@@ -589,7 +589,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
     <row r="20" hidden="1" outlineLevel="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 筛选"大于100"时只有数字123会被筛出来，文本"123"不参与数值比较。一眼分辨看对齐方式：文本左对齐、数字右对齐（左上角有绿色小三角提示的也是文本）。</t>
+          <t>答案: 筛选"大于100"时只有数字123会被筛出来，文本"123"不参与数值比较。一眼分辨看对齐方式：文本左对齐、数字右对齐（左上角有绿色小三角提示的也是文本）。</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="23" hidden="1" outlineLevel="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 数据没有统一规律时，补出来的结果是错的。补完之后必须从上到下扫一眼全部结果，不对的单元格手动改。</t>
+          <t>答案: 数据没有统一规律时，补出来的结果是错的。补完之后必须从上到下扫一眼全部结果，不对的单元格手动改。</t>
         </is>
       </c>
     </row>
